--- a/data/trans_orig/P70C2_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P70C2_2023-Clase-trans_orig.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W53"/>
+  <dimension ref="A1:W46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le es dificil cumplir con las obligaciones familiares debido al tiempo que paso en el trabajo en 2023</t>
+          <t>Población según si le es dificil cumplir con las obligaciones familiares debido al tiempo que paso en el trabajo en 2023 (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>188121</t>
+          <t>187908</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>227872</t>
+          <t>226125</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>53,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>159669</t>
+          <t>159890</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>190681</t>
+          <t>190785</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>60,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>359011</t>
+          <t>358630</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>410056</t>
+          <t>408540</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>53,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>61,1%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59807</t>
+          <t>59540</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>93193</t>
+          <t>91245</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53641</t>
+          <t>53969</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>77138</t>
+          <t>77720</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>120733</t>
+          <t>119974</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>161062</t>
+          <t>160886</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,06%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18828</t>
+          <t>18214</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>44923</t>
+          <t>44647</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>19253</t>
+          <t>19342</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>35468</t>
+          <t>35693</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>43258</t>
+          <t>43156</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>70468</t>
+          <t>73143</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,94%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14833</t>
+          <t>14606</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34179</t>
+          <t>34299</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17197</t>
+          <t>17476</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34987</t>
+          <t>33570</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36862</t>
+          <t>37004</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>61863</t>
+          <t>62889</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5551</t>
+          <t>5240</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19801</t>
+          <t>18896</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13459</t>
+          <t>13152</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>29200</t>
+          <t>28339</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>21409</t>
+          <t>21077</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>41594</t>
+          <t>43403</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2680</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14046</t>
+          <t>13125</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3155</t>
+          <t>2795</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12262</t>
+          <t>11391</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>7292</t>
+          <t>7341</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>20576</t>
+          <t>21834</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>143243</t>
+          <t>143984</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>182199</t>
+          <t>181363</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>47,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>136195</t>
+          <t>134680</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>162334</t>
+          <t>162937</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>53,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>64,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>287360</t>
+          <t>289256</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>334242</t>
+          <t>334937</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>52,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>60,55%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>60942</t>
+          <t>62939</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>94906</t>
+          <t>95264</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>47427</t>
+          <t>46452</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>70043</t>
+          <t>69586</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>117891</t>
+          <t>116726</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>156310</t>
+          <t>154341</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>27,9%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12713</t>
+          <t>13013</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31926</t>
+          <t>31567</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8180</t>
+          <t>8506</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20968</t>
+          <t>21364</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25099</t>
+          <t>24628</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47631</t>
+          <t>49015</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,86%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15075</t>
+          <t>15566</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38787</t>
+          <t>38773</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10209</t>
+          <t>10226</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25476</t>
+          <t>26137</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>27693</t>
+          <t>29748</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>54938</t>
+          <t>55077</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,96%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4317</t>
+          <t>4099</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16398</t>
+          <t>17452</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5978</t>
+          <t>5875</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17642</t>
+          <t>17054</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>11684</t>
+          <t>12006</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>29420</t>
+          <t>28351</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>2745</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14161</t>
+          <t>14443</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1834</t>
+          <t>1761</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10412</t>
+          <t>9813</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5397</t>
+          <t>5761</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20369</t>
+          <t>20704</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>234969</t>
+          <t>231333</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>458225</t>
+          <t>456093</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>29535</t>
+          <t>30002</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>44344</t>
+          <t>44380</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>61,22%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>269465</t>
+          <t>273808</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>509940</t>
+          <t>510816</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,86%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13842</t>
+          <t>13868</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>116997</t>
+          <t>117642</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10546</t>
+          <t>9939</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21885</t>
+          <t>21425</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>20166</t>
+          <t>23098</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>132966</t>
+          <t>130336</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,18%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2487</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>32508</t>
+          <t>31754</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>906</t>
+          <t>973</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5832</t>
+          <t>6099</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4909</t>
+          <t>3574</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>35568</t>
+          <t>33394</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4800</t>
+          <t>6590</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>55205</t>
+          <t>56260</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4103</t>
+          <t>4483</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12546</t>
+          <t>13695</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>9824</t>
+          <t>8671</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>64820</t>
+          <t>64434</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,46%</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4225</t>
+          <t>3424</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40517</t>
+          <t>42137</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3954</t>
+          <t>3945</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18508</t>
+          <t>17144</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6957</t>
+          <t>5616</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>52448</t>
+          <t>53530</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,52%</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2296</t>
+          <t>1932</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>27584</t>
+          <t>27834</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2900,12 +2900,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4201</t>
+          <t>3843</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3506</t>
+          <t>2491</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>27070</t>
+          <t>27061</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>204328</t>
+          <t>206352</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>258168</t>
+          <t>256080</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>167393</t>
+          <t>167969</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>202414</t>
+          <t>205059</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>385420</t>
+          <t>385150</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>450838</t>
+          <t>450986</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>45,86%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>107312</t>
+          <t>105050</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>155721</t>
+          <t>152964</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>84593</t>
+          <t>85291</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>115434</t>
+          <t>115631</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>198915</t>
+          <t>199727</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>258482</t>
+          <t>255893</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,02%</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>51824</t>
+          <t>50793</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>89239</t>
+          <t>87788</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>29805</t>
+          <t>28416</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>50895</t>
+          <t>49596</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>87981</t>
+          <t>87409</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>129762</t>
+          <t>129104</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,13%</t>
         </is>
       </c>
     </row>
@@ -3454,12 +3454,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>52501</t>
+          <t>54843</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>89723</t>
+          <t>89749</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>41220</t>
+          <t>39886</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>63467</t>
+          <t>63365</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>101479</t>
+          <t>102489</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>142482</t>
+          <t>143559</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,6%</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>32536</t>
+          <t>32530</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>63817</t>
+          <t>64547</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>28383</t>
+          <t>28604</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>50638</t>
+          <t>49293</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>67440</t>
+          <t>67036</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>102380</t>
+          <t>104163</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,59%</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>11744</t>
+          <t>12160</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>31366</t>
+          <t>31535</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>7184</t>
+          <t>7339</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>18600</t>
+          <t>18759</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>21613</t>
+          <t>22373</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>44473</t>
+          <t>44078</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>110175</t>
+          <t>110817</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>146031</t>
+          <t>147128</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>60,83%</t>
+          <t>61,28%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>163070</t>
+          <t>162743</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>284456</t>
+          <t>290643</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,17 +3975,17 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>346793</t>
+          <t>346794</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>296182</t>
+          <t>294654</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>437731</t>
+          <t>429743</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>48,01%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>70,03%</t>
         </is>
       </c>
     </row>
@@ -4023,12 +4023,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>43445</t>
+          <t>43395</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>72238</t>
+          <t>72679</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4038,12 +4038,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>36136</t>
+          <t>37612</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>92361</t>
+          <t>94007</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>80127</t>
+          <t>83021</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>153653</t>
+          <t>151129</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>24,63%</t>
         </is>
       </c>
     </row>
@@ -4136,12 +4136,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>8549</t>
+          <t>8314</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>28768</t>
+          <t>28809</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4151,12 +4151,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>16607</t>
+          <t>16018</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>45185</t>
+          <t>45475</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>30325</t>
+          <t>31189</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>62097</t>
+          <t>63860</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,41%</t>
         </is>
       </c>
     </row>
@@ -4249,12 +4249,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>15430</t>
+          <t>15102</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>39201</t>
+          <t>39191</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>12111</t>
+          <t>12493</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>35575</t>
+          <t>36924</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>31671</t>
+          <t>31262</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>65656</t>
+          <t>65555</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,68%</t>
         </is>
       </c>
     </row>
@@ -4362,12 +4362,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>4895</t>
+          <t>4385</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>17458</t>
+          <t>17747</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4377,12 +4377,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>9253</t>
+          <t>8542</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>29362</t>
+          <t>28309</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>17026</t>
+          <t>16866</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>40381</t>
+          <t>39153</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -4475,12 +4475,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>12306</t>
+          <t>12280</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4490,12 +4490,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>6316</t>
+          <t>6615</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>37244</t>
+          <t>37751</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4540,17 +4540,17 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>20801</t>
+          <t>20802</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>10591</t>
+          <t>11555</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>42009</t>
+          <t>41214</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -4653,17 +4653,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>613679</t>
+          <t>613680</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>613679</t>
+          <t>613680</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>613679</t>
+          <t>613680</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4685,7 +4685,7 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -4695,107 +4695,107 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>812</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1096504</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>963946</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1408297</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>955</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>765156</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>708277</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>868367</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1767</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1861661</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1711445</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2224988</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>50,62%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>65,8%</t>
         </is>
       </c>
     </row>
@@ -4808,107 +4808,107 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>406</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>388221</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>252548</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>459410</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>502</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>305332</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>253188</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>337619</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>908</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>693552</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>533260</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>773013</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,86%</t>
         </is>
       </c>
     </row>
@@ -4921,107 +4921,107 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>139</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>147073</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>96108</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>181322</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>174</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>113146</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>92902</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>133467</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>313</t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>260219</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>203400</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>300007</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,87%</t>
         </is>
       </c>
     </row>
@@ -5034,107 +5034,107 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>152</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>166908</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>108946</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>205796</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>183</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>123490</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>101259</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>144948</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>335</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>290398</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>218135</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>332113</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,82%</t>
         </is>
       </c>
     </row>
@@ -5147,107 +5147,107 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>88</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>92429</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>61327</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>115505</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>130</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>93416</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>74787</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>115183</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>218</t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>185845</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>142162</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>216270</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -5260,107 +5260,107 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>50223</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>31603</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>66862</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>39288</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>27938</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>60670</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>102</t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>89510</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>65767</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>111904</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -5373,919 +5373,123 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1647</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1941357</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1941357</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1941357</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1439828</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1439828</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1439828</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3643</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3381185</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3381185</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3381185</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>Nunca/ casi nunca</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>812</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>1096504</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>956788</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>1402755</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>56,48%</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>49,28%</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>72,26%</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>955</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>765156</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>708507</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>882791</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>53,14%</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t>49,21%</t>
-        </is>
-      </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t>61,31%</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t>1767</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t>1861661</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t>1708107</t>
-        </is>
-      </c>
-      <c r="T46" s="2" t="inlineStr">
-        <is>
-          <t>2200954</t>
-        </is>
-      </c>
-      <c r="U46" s="2" t="inlineStr">
-        <is>
-          <t>55,06%</t>
-        </is>
-      </c>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t>50,52%</t>
-        </is>
-      </c>
-      <c r="W46" s="2" t="inlineStr">
-        <is>
-          <t>65,09%</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="n"/>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>Con menos frecuencia /raramente</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>406</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>388221</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>258077</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>457524</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>20,0%</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>13,29%</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>23,57%</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>502</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>305332</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>255104</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>338988</t>
-        </is>
-      </c>
-      <c r="N47" s="2" t="inlineStr">
-        <is>
-          <t>21,21%</t>
-        </is>
-      </c>
-      <c r="O47" s="2" t="inlineStr">
-        <is>
-          <t>17,72%</t>
-        </is>
-      </c>
-      <c r="P47" s="2" t="inlineStr">
-        <is>
-          <t>23,54%</t>
-        </is>
-      </c>
-      <c r="Q47" s="2" t="inlineStr">
-        <is>
-          <t>908</t>
-        </is>
-      </c>
-      <c r="R47" s="2" t="inlineStr">
-        <is>
-          <t>693552</t>
-        </is>
-      </c>
-      <c r="S47" s="2" t="inlineStr">
-        <is>
-          <t>537639</t>
-        </is>
-      </c>
-      <c r="T47" s="2" t="inlineStr">
-        <is>
-          <t>773735</t>
-        </is>
-      </c>
-      <c r="U47" s="2" t="inlineStr">
-        <is>
-          <t>20,51%</t>
-        </is>
-      </c>
-      <c r="V47" s="2" t="inlineStr">
-        <is>
-          <t>15,9%</t>
-        </is>
-      </c>
-      <c r="W47" s="2" t="inlineStr">
-        <is>
-          <t>22,88%</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="n"/>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>Varias veces al año</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>147073</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>88055</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>183154</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>7,58%</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>4,54%</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>9,43%</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>113146</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>93004</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>134091</t>
-        </is>
-      </c>
-      <c r="N48" s="2" t="inlineStr">
-        <is>
-          <t>7,86%</t>
-        </is>
-      </c>
-      <c r="O48" s="2" t="inlineStr">
-        <is>
-          <t>6,46%</t>
-        </is>
-      </c>
-      <c r="P48" s="2" t="inlineStr">
-        <is>
-          <t>9,31%</t>
-        </is>
-      </c>
-      <c r="Q48" s="2" t="inlineStr">
-        <is>
-          <t>313</t>
-        </is>
-      </c>
-      <c r="R48" s="2" t="inlineStr">
-        <is>
-          <t>260219</t>
-        </is>
-      </c>
-      <c r="S48" s="2" t="inlineStr">
-        <is>
-          <t>203341</t>
-        </is>
-      </c>
-      <c r="T48" s="2" t="inlineStr">
-        <is>
-          <t>302870</t>
-        </is>
-      </c>
-      <c r="U48" s="2" t="inlineStr">
-        <is>
-          <t>7,7%</t>
-        </is>
-      </c>
-      <c r="V48" s="2" t="inlineStr">
-        <is>
-          <t>6,01%</t>
-        </is>
-      </c>
-      <c r="W48" s="2" t="inlineStr">
-        <is>
-          <t>8,96%</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="n"/>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>Varias veces al mes</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>166908</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>100839</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>203376</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>8,6%</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>5,19%</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>10,48%</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>123490</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>102482</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t>146478</t>
-        </is>
-      </c>
-      <c r="N49" s="2" t="inlineStr">
-        <is>
-          <t>8,58%</t>
-        </is>
-      </c>
-      <c r="O49" s="2" t="inlineStr">
-        <is>
-          <t>7,12%</t>
-        </is>
-      </c>
-      <c r="P49" s="2" t="inlineStr">
-        <is>
-          <t>10,17%</t>
-        </is>
-      </c>
-      <c r="Q49" s="2" t="inlineStr">
-        <is>
-          <t>335</t>
-        </is>
-      </c>
-      <c r="R49" s="2" t="inlineStr">
-        <is>
-          <t>290398</t>
-        </is>
-      </c>
-      <c r="S49" s="2" t="inlineStr">
-        <is>
-          <t>224177</t>
-        </is>
-      </c>
-      <c r="T49" s="2" t="inlineStr">
-        <is>
-          <t>332659</t>
-        </is>
-      </c>
-      <c r="U49" s="2" t="inlineStr">
-        <is>
-          <t>8,59%</t>
-        </is>
-      </c>
-      <c r="V49" s="2" t="inlineStr">
-        <is>
-          <t>6,63%</t>
-        </is>
-      </c>
-      <c r="W49" s="2" t="inlineStr">
-        <is>
-          <t>9,84%</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="n"/>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>Varias veces a la semana</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>92429</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>57197</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>117623</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>4,76%</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>2,95%</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>6,06%</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>93416</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>74601</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t>113993</t>
-        </is>
-      </c>
-      <c r="N50" s="2" t="inlineStr">
-        <is>
-          <t>6,49%</t>
-        </is>
-      </c>
-      <c r="O50" s="2" t="inlineStr">
-        <is>
-          <t>5,18%</t>
-        </is>
-      </c>
-      <c r="P50" s="2" t="inlineStr">
-        <is>
-          <t>7,92%</t>
-        </is>
-      </c>
-      <c r="Q50" s="2" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
-      <c r="R50" s="2" t="inlineStr">
-        <is>
-          <t>185845</t>
-        </is>
-      </c>
-      <c r="S50" s="2" t="inlineStr">
-        <is>
-          <t>141996</t>
-        </is>
-      </c>
-      <c r="T50" s="2" t="inlineStr">
-        <is>
-          <t>219155</t>
-        </is>
-      </c>
-      <c r="U50" s="2" t="inlineStr">
-        <is>
-          <t>5,5%</t>
-        </is>
-      </c>
-      <c r="V50" s="2" t="inlineStr">
-        <is>
-          <t>4,2%</t>
-        </is>
-      </c>
-      <c r="W50" s="2" t="inlineStr">
-        <is>
-          <t>6,48%</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="n"/>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>A diario</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>50223</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>32497</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>67026</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>2,59%</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>3,45%</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>39288</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>28563</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>61978</t>
-        </is>
-      </c>
-      <c r="N51" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
-      <c r="O51" s="2" t="inlineStr">
-        <is>
-          <t>1,98%</t>
-        </is>
-      </c>
-      <c r="P51" s="2" t="inlineStr">
-        <is>
-          <t>4,3%</t>
-        </is>
-      </c>
-      <c r="Q51" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="R51" s="2" t="inlineStr">
-        <is>
-          <t>89510</t>
-        </is>
-      </c>
-      <c r="S51" s="2" t="inlineStr">
-        <is>
-          <t>66556</t>
-        </is>
-      </c>
-      <c r="T51" s="2" t="inlineStr">
-        <is>
-          <t>114098</t>
-        </is>
-      </c>
-      <c r="U51" s="2" t="inlineStr">
-        <is>
-          <t>2,65%</t>
-        </is>
-      </c>
-      <c r="V51" s="2" t="inlineStr">
-        <is>
-          <t>1,97%</t>
-        </is>
-      </c>
-      <c r="W51" s="2" t="inlineStr">
-        <is>
-          <t>3,37%</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="n"/>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>1647</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>1941357</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>1941357</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>1941357</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>1996</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>1439828</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>1439828</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr">
-        <is>
-          <t>1439828</t>
-        </is>
-      </c>
-      <c r="N52" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O52" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P52" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q52" s="2" t="inlineStr">
-        <is>
-          <t>3643</t>
-        </is>
-      </c>
-      <c r="R52" s="2" t="inlineStr">
-        <is>
-          <t>3381185</t>
-        </is>
-      </c>
-      <c r="S52" s="2" t="inlineStr">
-        <is>
-          <t>3381185</t>
-        </is>
-      </c>
-      <c r="T52" s="2" t="inlineStr">
-        <is>
-          <t>3381185</t>
-        </is>
-      </c>
-      <c r="U52" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V52" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W52" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A46" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A32:A38"/>
     <mergeCell ref="A4:A10"/>
     <mergeCell ref="A25:A31"/>
-    <mergeCell ref="A46:A52"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>

--- a/data/trans_orig/P70C2_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P70C2_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>208602</t>
+          <t>225369</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>187908</t>
+          <t>205172</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>226125</t>
+          <t>247998</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>59,28%</t>
+          <t>58,87%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>53,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>174702</t>
+          <t>185872</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>159890</t>
+          <t>168993</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>190785</t>
+          <t>201519</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>59,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>383303</t>
+          <t>411242</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>358630</t>
+          <t>384192</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>408540</t>
+          <t>435850</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>57,03%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>53,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>60,45%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>74393</t>
+          <t>80807</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59540</t>
+          <t>65469</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>91245</t>
+          <t>98368</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>64842</t>
+          <t>68994</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53969</t>
+          <t>57969</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>77720</t>
+          <t>82358</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>139235</t>
+          <t>149802</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>119974</t>
+          <t>130135</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>160886</t>
+          <t>172208</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,88%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>29021</t>
+          <t>29113</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18214</t>
+          <t>20218</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>44647</t>
+          <t>43847</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>26641</t>
+          <t>28570</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>19342</t>
+          <t>20285</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>35693</t>
+          <t>36736</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>55662</t>
+          <t>57683</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>43156</t>
+          <t>44186</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>73143</t>
+          <t>74458</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,33%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23061</t>
+          <t>29693</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14606</t>
+          <t>19791</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34299</t>
+          <t>43952</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24667</t>
+          <t>27373</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17476</t>
+          <t>19509</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33570</t>
+          <t>37743</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>47729</t>
+          <t>57067</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37004</t>
+          <t>42715</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>62889</t>
+          <t>73009</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>10,13%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>10405</t>
+          <t>10827</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5240</t>
+          <t>5423</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18896</t>
+          <t>21043</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>19664</t>
+          <t>20878</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13152</t>
+          <t>14012</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>28339</t>
+          <t>31334</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>30068</t>
+          <t>31705</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>21077</t>
+          <t>22348</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>43403</t>
+          <t>44131</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6431</t>
+          <t>7002</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>2452</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13125</t>
+          <t>14360</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,32 +1325,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>6563</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2795</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11391</t>
+          <t>11654</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>12695</t>
+          <t>13566</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>7341</t>
+          <t>8029</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>21834</t>
+          <t>23830</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>351913</t>
+          <t>382812</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>351913</t>
+          <t>382812</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>351913</t>
+          <t>382812</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,17 +1438,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>316779</t>
+          <t>338251</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>316779</t>
+          <t>338251</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>316779</t>
+          <t>338251</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,17 +1473,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>668691</t>
+          <t>721064</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>668691</t>
+          <t>721064</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>668691</t>
+          <t>721064</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>162403</t>
+          <t>169797</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>143984</t>
+          <t>149897</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>181363</t>
+          <t>188515</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>59,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>149312</t>
+          <t>162110</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>134680</t>
+          <t>146808</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>162937</t>
+          <t>175851</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>311717</t>
+          <t>331906</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>289256</t>
+          <t>307092</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>334937</t>
+          <t>355393</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>60,08%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>77735</t>
+          <t>83083</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>62939</t>
+          <t>66730</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>95264</t>
+          <t>101737</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>57751</t>
+          <t>63377</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46452</t>
+          <t>52457</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>69586</t>
+          <t>75911</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>135486</t>
+          <t>146460</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>116726</t>
+          <t>126997</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>154341</t>
+          <t>169922</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>28,73%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>20868</t>
+          <t>22614</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13013</t>
+          <t>13969</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31567</t>
+          <t>34915</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13792</t>
+          <t>14961</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8506</t>
+          <t>9548</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21364</t>
+          <t>22732</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>34660</t>
+          <t>37575</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24628</t>
+          <t>26722</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>49015</t>
+          <t>51593</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -1859,22 +1859,22 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>24310</t>
+          <t>25140</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15566</t>
+          <t>16462</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38773</t>
+          <t>39457</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>16297</t>
+          <t>16726</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10226</t>
+          <t>10417</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26137</t>
+          <t>25821</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>40607</t>
+          <t>41866</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>29748</t>
+          <t>30110</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>55077</t>
+          <t>57392</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,7%</t>
         </is>
       </c>
     </row>
@@ -1972,32 +1972,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8906</t>
+          <t>10286</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4099</t>
+          <t>4689</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17452</t>
+          <t>18658</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2007,32 +2007,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10348</t>
+          <t>11356</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5875</t>
+          <t>6297</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17054</t>
+          <t>18228</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>19255</t>
+          <t>21642</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>12006</t>
+          <t>13841</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>28351</t>
+          <t>32242</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -2085,32 +2085,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>6761</t>
+          <t>7195</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2745</t>
+          <t>2614</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14443</t>
+          <t>15974</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,32 +2120,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4666</t>
+          <t>4873</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1761</t>
+          <t>2118</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9813</t>
+          <t>10769</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>11426</t>
+          <t>12068</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5761</t>
+          <t>5979</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20704</t>
+          <t>20961</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -2198,17 +2198,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>300983</t>
+          <t>318115</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>300983</t>
+          <t>318115</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>300983</t>
+          <t>318115</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,17 +2233,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>252166</t>
+          <t>273404</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>252166</t>
+          <t>273404</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>252166</t>
+          <t>273404</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,17 +2268,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>553150</t>
+          <t>591518</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>553150</t>
+          <t>591518</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>553150</t>
+          <t>591518</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>366508</t>
+          <t>136721</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>231333</t>
+          <t>119209</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>456093</t>
+          <t>155352</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>50,19%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>57,03%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>37544</t>
+          <t>43677</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>30002</t>
+          <t>34451</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>44380</t>
+          <t>50851</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>53,11%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>61,22%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>404052</t>
+          <t>180398</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>273808</t>
+          <t>160667</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>510816</t>
+          <t>199022</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>56,12%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>54462</t>
+          <t>61534</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13868</t>
+          <t>47769</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>117642</t>
+          <t>77640</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>15365</t>
+          <t>17324</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9939</t>
+          <t>11528</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21425</t>
+          <t>24599</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>69826</t>
+          <t>78858</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23098</t>
+          <t>64357</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>130336</t>
+          <t>95739</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>26,99%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>14201</t>
+          <t>14783</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2487</t>
+          <t>8452</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>31754</t>
+          <t>24469</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2630</t>
+          <t>2711</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>898</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6099</t>
+          <t>6091</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>16831</t>
+          <t>17494</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3574</t>
+          <t>10990</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>33394</t>
+          <t>27022</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -2654,32 +2654,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>24703</t>
+          <t>25402</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6590</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>56260</t>
+          <t>39395</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2689,32 +2689,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7872</t>
+          <t>8654</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4483</t>
+          <t>4760</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13695</t>
+          <t>14232</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>32574</t>
+          <t>34056</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>8671</t>
+          <t>24272</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>64434</t>
+          <t>48024</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>13,54%</t>
         </is>
       </c>
     </row>
@@ -2767,32 +2767,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>18007</t>
+          <t>19373</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3424</t>
+          <t>12049</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>42137</t>
+          <t>31440</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2802,32 +2802,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>7968</t>
+          <t>8751</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3945</t>
+          <t>4234</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17144</t>
+          <t>19407</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,32 +2837,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>25975</t>
+          <t>28125</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5616</t>
+          <t>18897</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>53530</t>
+          <t>43296</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>12,21%</t>
         </is>
       </c>
     </row>
@@ -2880,32 +2880,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>11807</t>
+          <t>14599</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1932</t>
+          <t>8128</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>27834</t>
+          <t>25338</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1110</t>
+          <t>1124</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3843</t>
+          <t>3801</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,32 +2950,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>12917</t>
+          <t>15722</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2491</t>
+          <t>8169</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>27061</t>
+          <t>25434</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
+          <t>4,43%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>2,3%</t>
         </is>
       </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -2993,17 +2993,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>489687</t>
+          <t>272413</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>489687</t>
+          <t>272413</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>489687</t>
+          <t>272413</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,17 +3028,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>72488</t>
+          <t>82241</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>72488</t>
+          <t>82241</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>72488</t>
+          <t>82241</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,17 +3063,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>562175</t>
+          <t>354654</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>562175</t>
+          <t>354654</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>562175</t>
+          <t>354654</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>230207</t>
+          <t>257725</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>206352</t>
+          <t>227074</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>256080</t>
+          <t>283482</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>185589</t>
+          <t>207596</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>167969</t>
+          <t>187221</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>205059</t>
+          <t>226975</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>415796</t>
+          <t>465321</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>385150</t>
+          <t>431779</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>450986</t>
+          <t>499752</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>45,56%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>125366</t>
+          <t>137332</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>105050</t>
+          <t>115410</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>152964</t>
+          <t>161437</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>99948</t>
+          <t>114700</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>85291</t>
+          <t>99368</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>115631</t>
+          <t>134113</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>225314</t>
+          <t>252033</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>199727</t>
+          <t>223060</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>255893</t>
+          <t>276180</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>25,18%</t>
         </is>
       </c>
     </row>
@@ -3336,32 +3336,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>67752</t>
+          <t>78538</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>50793</t>
+          <t>61762</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>87788</t>
+          <t>102248</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3371,32 +3371,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>38579</t>
+          <t>42621</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>28416</t>
+          <t>31492</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>49596</t>
+          <t>54105</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>106331</t>
+          <t>121159</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>87409</t>
+          <t>100072</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>129104</t>
+          <t>144924</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,21%</t>
         </is>
       </c>
     </row>
@@ -3449,32 +3449,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>70078</t>
+          <t>73131</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>54843</t>
+          <t>56148</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>89749</t>
+          <t>92982</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3484,32 +3484,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>51356</t>
+          <t>55826</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>39886</t>
+          <t>44425</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>63365</t>
+          <t>68003</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>121434</t>
+          <t>128957</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>102489</t>
+          <t>109282</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>143559</t>
+          <t>153341</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>13,98%</t>
         </is>
       </c>
     </row>
@@ -3562,32 +3562,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>45623</t>
+          <t>48621</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>32530</t>
+          <t>35287</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>64547</t>
+          <t>65990</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3597,32 +3597,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>37321</t>
+          <t>41105</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>28604</t>
+          <t>31800</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>49293</t>
+          <t>53526</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>82944</t>
+          <t>89726</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>67036</t>
+          <t>74549</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>104163</t>
+          <t>112477</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,25%</t>
         </is>
       </c>
     </row>
@@ -3675,32 +3675,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>19671</t>
+          <t>24308</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>12160</t>
+          <t>15886</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>31535</t>
+          <t>37738</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3710,32 +3710,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>12000</t>
+          <t>15519</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>7339</t>
+          <t>9948</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>18759</t>
+          <t>23774</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>31671</t>
+          <t>39827</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>22373</t>
+          <t>27585</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>44078</t>
+          <t>53806</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -3788,17 +3788,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>558696</t>
+          <t>619655</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>558696</t>
+          <t>619655</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>558696</t>
+          <t>619655</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>424792</t>
+          <t>477367</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>424792</t>
+          <t>477367</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>424792</t>
+          <t>477367</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3858,17 +3858,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>983489</t>
+          <t>1097022</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>983489</t>
+          <t>1097022</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>983489</t>
+          <t>1097022</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>128784</t>
+          <t>170871</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>110817</t>
+          <t>149048</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>147128</t>
+          <t>190770</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>53,64%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>218010</t>
+          <t>138581</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>162743</t>
+          <t>123268</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>290643</t>
+          <t>154743</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>346794</t>
+          <t>309452</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>294654</t>
+          <t>283215</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>429743</t>
+          <t>336550</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>54,05%</t>
         </is>
       </c>
     </row>
@@ -4018,32 +4018,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>56265</t>
+          <t>74395</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>43395</t>
+          <t>59273</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>72679</t>
+          <t>94071</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4053,32 +4053,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>67427</t>
+          <t>75920</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>37612</t>
+          <t>63381</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>94007</t>
+          <t>89433</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4088,32 +4088,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>123691</t>
+          <t>150315</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>83021</t>
+          <t>127758</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>151129</t>
+          <t>171525</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>27,55%</t>
         </is>
       </c>
     </row>
@@ -4131,32 +4131,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>15231</t>
+          <t>18725</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>8314</t>
+          <t>10479</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>28809</t>
+          <t>33963</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4166,32 +4166,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>31505</t>
+          <t>37126</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>16018</t>
+          <t>28473</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>45475</t>
+          <t>47491</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4201,32 +4201,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>46736</t>
+          <t>55851</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>31189</t>
+          <t>42997</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>63860</t>
+          <t>72340</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>11,62%</t>
         </is>
       </c>
     </row>
@@ -4244,32 +4244,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>24756</t>
+          <t>27711</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>15102</t>
+          <t>18071</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>39191</t>
+          <t>42460</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4279,32 +4279,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>23298</t>
+          <t>27644</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>12493</t>
+          <t>19846</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>36924</t>
+          <t>37494</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4314,32 +4314,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>48054</t>
+          <t>55355</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>31262</t>
+          <t>43426</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>65555</t>
+          <t>71841</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>11,54%</t>
         </is>
       </c>
     </row>
@@ -4357,32 +4357,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>9488</t>
+          <t>10487</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>4385</t>
+          <t>5057</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>17747</t>
+          <t>17896</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4392,32 +4392,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>18115</t>
+          <t>23266</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>8542</t>
+          <t>16646</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>28309</t>
+          <t>34141</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4427,32 +4427,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>27603</t>
+          <t>33753</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>16866</t>
+          <t>23699</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>39153</t>
+          <t>47040</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -4470,32 +4470,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>5553</t>
+          <t>6725</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2675</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>12280</t>
+          <t>15361</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4505,67 +4505,67 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>15248</t>
+          <t>11188</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>6615</t>
+          <t>6359</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>37751</t>
+          <t>18462</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
+          <t>2,03%</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>5,88%</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>17913</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>11012</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>26770</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>2,88%</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
           <t>1,77%</t>
         </is>
       </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>10,1%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>20802</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>11555</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>41214</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>3,39%</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>1,88%</t>
-        </is>
-      </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -4583,17 +4583,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>240077</t>
+          <t>308914</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>240077</t>
+          <t>308914</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>240077</t>
+          <t>308914</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4618,17 +4618,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>373603</t>
+          <t>313726</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>373603</t>
+          <t>313726</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>373603</t>
+          <t>313726</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4653,17 +4653,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>613680</t>
+          <t>622640</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>613680</t>
+          <t>622640</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>613680</t>
+          <t>622640</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4700,32 +4700,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>1096504</t>
+          <t>960483</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>963946</t>
+          <t>908799</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>1408297</t>
+          <t>1009940</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4735,32 +4735,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>765156</t>
+          <t>737836</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>708277</t>
+          <t>700646</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>868367</t>
+          <t>771012</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4770,32 +4770,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>1861661</t>
+          <t>1698319</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1711445</t>
+          <t>1635196</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>2224988</t>
+          <t>1757180</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>51,88%</t>
         </is>
       </c>
     </row>
@@ -4813,32 +4813,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>388221</t>
+          <t>437152</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>252548</t>
+          <t>400833</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>459410</t>
+          <t>479889</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4848,32 +4848,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>305332</t>
+          <t>340316</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>253188</t>
+          <t>311772</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>337619</t>
+          <t>368882</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4883,32 +4883,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>693552</t>
+          <t>777468</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>533260</t>
+          <t>729924</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>773013</t>
+          <t>829043</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>24,48%</t>
         </is>
       </c>
     </row>
@@ -4926,32 +4926,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>147073</t>
+          <t>163774</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>96108</t>
+          <t>136532</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>181322</t>
+          <t>194141</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4961,32 +4961,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>113146</t>
+          <t>125988</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>92902</t>
+          <t>108502</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>133467</t>
+          <t>146060</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4996,32 +4996,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>260219</t>
+          <t>289762</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>203400</t>
+          <t>260058</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>300007</t>
+          <t>327697</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,68%</t>
         </is>
       </c>
     </row>
@@ -5039,32 +5039,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>166908</t>
+          <t>181078</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>108946</t>
+          <t>155733</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>205796</t>
+          <t>211198</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5074,32 +5074,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>123490</t>
+          <t>136224</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>101259</t>
+          <t>119729</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>144948</t>
+          <t>160030</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5109,32 +5109,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>290398</t>
+          <t>317302</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>218135</t>
+          <t>286372</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>332113</t>
+          <t>357426</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,55%</t>
         </is>
       </c>
     </row>
@@ -5152,32 +5152,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>92429</t>
+          <t>99594</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>61327</t>
+          <t>79072</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>115505</t>
+          <t>124298</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5187,32 +5187,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>93416</t>
+          <t>105357</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>74787</t>
+          <t>88737</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>115183</t>
+          <t>127208</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5222,32 +5222,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>185845</t>
+          <t>204951</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>142162</t>
+          <t>178412</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>216270</t>
+          <t>237644</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -5265,32 +5265,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>50223</t>
+          <t>59829</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>31603</t>
+          <t>43824</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>66862</t>
+          <t>80486</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5300,32 +5300,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>39288</t>
+          <t>39268</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>27938</t>
+          <t>29429</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>60670</t>
+          <t>51559</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5335,32 +5335,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>89510</t>
+          <t>99096</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>65767</t>
+          <t>82396</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>111904</t>
+          <t>120561</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -5378,17 +5378,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>1941357</t>
+          <t>1901909</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>1941357</t>
+          <t>1901909</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>1941357</t>
+          <t>1901909</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5413,17 +5413,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>1439828</t>
+          <t>1484989</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>1439828</t>
+          <t>1484989</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>1439828</t>
+          <t>1484989</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5448,17 +5448,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>3381185</t>
+          <t>3386898</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>3381185</t>
+          <t>3386898</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>3381185</t>
+          <t>3386898</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
